--- a/Warehouse_ABC_SKU_template.xlsx
+++ b/Warehouse_ABC_SKU_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeromy\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BEB742-826E-46F2-824C-33C9F5F486CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B53CC6-EEDF-4396-B084-1A2E42427ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使用說明" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="181">
   <si>
-    <t>倉儲 ABC 儲位分析 Excel Template（無特定客戶名稱版）</t>
-  </si>
-  <si>
     <t>用途</t>
   </si>
   <si>
@@ -41,9 +38,6 @@
   </si>
   <si>
     <t>主要作業區</t>
-  </si>
-  <si>
-    <t>原本特定客戶作業區字眼已移除，統一改為「主要作業區」，可泛用於任何倉儲場域。</t>
   </si>
   <si>
     <t>Colab 分析</t>
@@ -573,7 +567,7 @@
       </rPr>
       <t>資料輸入</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -633,7 +627,7 @@
       </rPr>
       <t>自動產生。</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -650,22 +644,65 @@
       </rPr>
       <t>程式欄位對照表</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要作業區，可泛用於任何倉儲場域。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>倉儲</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ABC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>儲位分析</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Excel Template</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -722,6 +759,35 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -762,18 +828,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -782,20 +848,23 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -993,63 +1062,63 @@
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+    <row r="1" spans="1:8" ht="20.5">
+      <c r="A1" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="14.5">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
+      <c r="B5" s="14" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1068,89 +1137,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="19.5">
-      <c r="A1" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+      <c r="A1" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" ht="14.5">
-      <c r="A2" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="A2" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D5" s="5">
         <v>260</v>
@@ -1159,39 +1228,39 @@
         <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L5" s="5">
         <v>60</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="5">
         <v>240</v>
@@ -1200,39 +1269,39 @@
         <v>115</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L6" s="5">
         <v>55</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5">
         <v>210</v>
@@ -1241,39 +1310,39 @@
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L7" s="5">
         <v>50</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5">
         <v>190</v>
@@ -1282,39 +1351,39 @@
         <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L8" s="5">
         <v>45</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5">
         <v>170</v>
@@ -1323,39 +1392,39 @@
         <v>86</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L9" s="5">
         <v>42</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D10" s="5">
         <v>150</v>
@@ -1364,39 +1433,39 @@
         <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L10" s="5">
         <v>40</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D11" s="5">
         <v>130</v>
@@ -1405,39 +1474,39 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L11" s="5">
         <v>38</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D12" s="5">
         <v>110</v>
@@ -1446,39 +1515,39 @@
         <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L12" s="5">
         <v>36</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5">
         <v>95</v>
@@ -1487,39 +1556,39 @@
         <v>55</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L13" s="5">
         <v>35</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" s="5">
         <v>88</v>
@@ -1528,39 +1597,39 @@
         <v>50</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L14" s="5">
         <v>34</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="5">
         <v>76</v>
@@ -1569,39 +1638,39 @@
         <v>45</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L15" s="5">
         <v>32</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="5">
         <v>70</v>
@@ -1610,39 +1679,39 @@
         <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L16" s="5">
         <v>30</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D17" s="5">
         <v>58</v>
@@ -1651,39 +1720,39 @@
         <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L17" s="5">
         <v>28</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D18" s="5">
         <v>52</v>
@@ -1692,39 +1761,39 @@
         <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L18" s="5">
         <v>27</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" s="5">
         <v>48</v>
@@ -1733,39 +1802,39 @@
         <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L19" s="5">
         <v>25</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" s="5">
         <v>42</v>
@@ -1774,39 +1843,39 @@
         <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L20" s="5">
         <v>22</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D21" s="5">
         <v>38</v>
@@ -1815,39 +1884,39 @@
         <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L21" s="5">
         <v>20</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" s="5">
         <v>34</v>
@@ -1856,39 +1925,39 @@
         <v>22</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L22" s="5">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D23" s="5">
         <v>30</v>
@@ -1897,39 +1966,39 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L23" s="5">
         <v>45</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="5">
         <v>28</v>
@@ -1938,39 +2007,39 @@
         <v>18</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L24" s="5">
         <v>48</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D25" s="5">
         <v>22</v>
@@ -1979,39 +2048,39 @@
         <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L25" s="5">
         <v>50</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D26" s="5">
         <v>18</v>
@@ -2020,39 +2089,39 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L26" s="5">
         <v>52</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D27" s="5">
         <v>15</v>
@@ -2061,39 +2130,39 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L27" s="5">
         <v>55</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D28" s="5">
         <v>12</v>
@@ -2102,39 +2171,39 @@
         <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L28" s="5">
         <v>58</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D29" s="5">
         <v>8</v>
@@ -2143,28 +2212,28 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L29" s="5">
         <v>60</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2172,7 +2241,7 @@
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="list" sqref="F5:F100" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"小,中,大"</formula1>
@@ -2206,102 +2275,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19">
-      <c r="A1" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="A1" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B4" s="6">
         <v>0.8</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B5" s="6">
         <v>0.95</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B6" s="7">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B7" s="7">
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B8" s="7">
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2319,393 +2388,393 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5">
-      <c r="A1" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="A1" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" t="s">
         <v>137</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" t="s">
         <v>138</v>
-      </c>
-      <c r="E5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" t="s">
         <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
         <v>161</v>
       </c>
-      <c r="B17" t="s">
+      <c r="E17" t="s">
         <v>162</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>